--- a/Data/Building/Lab.Brightness.xlsx
+++ b/Data/Building/Lab.Brightness.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709252300</v>
+        <v>1711843370</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709252320</v>
+        <v>1711844066</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709252341</v>
+        <v>1711851118</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709275957</v>
+        <v>1711869187</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709275991</v>
+        <v>1711869207</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709276010</v>
+        <v>1711869226</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709276073</v>
+        <v>1711869268</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +704,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709276100</v>
+        <v>1711869297</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +737,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709276129</v>
+        <v>1711930046</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +770,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709266728</v>
+        <v>1711945087</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +803,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709266749</v>
+        <v>1711945104</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +836,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709266775</v>
+        <v>1711945129</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +869,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709266819</v>
+        <v>1711945168</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +902,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +921,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709266846</v>
+        <v>1711945194</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +935,7 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +954,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709266862</v>
+        <v>1711945221</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +968,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +987,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709354105</v>
+        <v>1712035296</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1001,7 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1020,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709354127</v>
+        <v>1712035319</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1034,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1053,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709354162</v>
+        <v>1712035346</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1086,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709354229</v>
+        <v>1712035396</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1100,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1119,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709354260</v>
+        <v>1712035420</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1133,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1152,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709354288</v>
+        <v>1712104256</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1166,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1185,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709442077</v>
+        <v>1712122840</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1199,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1218,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709442101</v>
+        <v>1712122868</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1232,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1251,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709442125</v>
+        <v>1712122893</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1265,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1284,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709442178</v>
+        <v>1712122928</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1298,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1317,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709442203</v>
+        <v>1712122946</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1331,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1350,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709442246</v>
+        <v>1712122967</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1364,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1383,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709527998</v>
+        <v>1712206545</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1397,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1416,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709528016</v>
+        <v>1712206572</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1430,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1449,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709528054</v>
+        <v>1712206594</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1463,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1482,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709528096</v>
+        <v>1712206642</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1496,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1515,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709528124</v>
+        <v>1712206665</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1529,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1548,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709597788</v>
+        <v>1712206686</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1562,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1581,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709616557</v>
+        <v>1712292722</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1595,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1614,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709616595</v>
+        <v>1712292751</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1628,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1647,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709616618</v>
+        <v>1712292773</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1661,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1680,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709616684</v>
+        <v>1712292820</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1694,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1713,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709616717</v>
+        <v>1712292843</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1727,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1746,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709616753</v>
+        <v>1712363744</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1760,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1779,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709870200</v>
+        <v>1712554878</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1793,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1812,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709870243</v>
+        <v>1712554920</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1826,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1845,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709870255</v>
+        <v>1712554941</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1859,7 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1878,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709870321</v>
+        <v>1712554989</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1892,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1911,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709870349</v>
+        <v>1712555015</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1925,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1944,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709870384</v>
+        <v>1712621574</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +1958,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1977,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709959843</v>
+        <v>1712638493</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +1991,7 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2010,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709959871</v>
+        <v>1712638520</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2024,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2043,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709959895</v>
+        <v>1712638560</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2057,7 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2076,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709959930</v>
+        <v>1712638630</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2090,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2109,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709959947</v>
+        <v>1712638665</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2123,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2142,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1710030658</v>
+        <v>1712638707</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2156,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2175,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710049103</v>
+        <v>1712724677</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2189,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2208,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710049129</v>
+        <v>1712724708</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2222,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2241,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710049157</v>
+        <v>1712724746</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2255,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2274,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710049214</v>
+        <v>1712724787</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2288,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2307,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710049241</v>
+        <v>1712724819</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2321,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2340,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710049265</v>
+        <v>1712724844</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2354,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2373,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710136438</v>
+        <v>1712811401</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2387,7 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2406,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710136464</v>
+        <v>1712811419</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2420,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2439,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710136504</v>
+        <v>1712811449</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2453,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2472,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710136552</v>
+        <v>1712811506</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2486,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2505,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1710136590</v>
+        <v>1712811532</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2519,7 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2538,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710136635</v>
+        <v>1712811567</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2552,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2571,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710220831</v>
+        <v>1712896248</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2585,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2604,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710220857</v>
+        <v>1712896280</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2618,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2637,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710220880</v>
+        <v>1712896300</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2651,7 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2670,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710220924</v>
+        <v>1712896342</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2684,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2703,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710220949</v>
+        <v>1712896374</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2717,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2736,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710220988</v>
+        <v>1712896395</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2750,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2769,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710478354</v>
+        <v>1713157032</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2783,7 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2802,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710478385</v>
+        <v>1713157054</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2816,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2835,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710478406</v>
+        <v>1713157087</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2849,7 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2868,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710478476</v>
+        <v>1713157136</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2882,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2901,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710478502</v>
+        <v>1713157170</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2915,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2934,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710478525</v>
+        <v>1713224811</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +2948,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +2967,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710565196</v>
+        <v>1713241300</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +2981,7 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3000,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710565239</v>
+        <v>1713241327</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3014,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3033,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710565270</v>
+        <v>1713241347</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3047,7 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3066,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710565321</v>
+        <v>1713241414</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3080,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3099,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710565357</v>
+        <v>1713241452</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3113,7 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3132,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710635602</v>
+        <v>1713241477</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3146,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3165,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710656349</v>
+        <v>1713326269</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3179,7 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3198,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710656378</v>
+        <v>1713326306</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3212,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3231,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710656406</v>
+        <v>1713326326</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3245,7 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3264,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710656462</v>
+        <v>1713326380</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3278,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3297,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710656492</v>
+        <v>1713326405</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3311,7 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3330,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710720247</v>
+        <v>1713326453</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3344,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3363,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710738282</v>
+        <v>1713412106</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3377,7 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3396,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710738326</v>
+        <v>1713412139</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3410,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3429,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710738367</v>
+        <v>1713412172</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3443,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3462,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710738417</v>
+        <v>1713412212</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3476,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3495,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710738440</v>
+        <v>1713412255</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3509,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3528,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710807511</v>
+        <v>1713412287</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3542,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3561,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710825822</v>
+        <v>1713501252</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3575,7 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3594,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710825855</v>
+        <v>1713501276</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3608,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3627,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710825887</v>
+        <v>1713501311</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3641,7 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3660,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710825958</v>
+        <v>1713501355</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3674,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3693,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710825990</v>
+        <v>1713501397</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3707,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3726,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710826021</v>
+        <v>1713572623</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3740,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3759,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1711084012</v>
+        <v>1713757280</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3773,7 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3792,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1711084039</v>
+        <v>1713757297</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3806,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3825,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1711084066</v>
+        <v>1713757326</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3839,7 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3858,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1711084116</v>
+        <v>1713757369</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +3872,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3891,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1711084135</v>
+        <v>1713757389</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,6 +3905,7 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3924,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1711084163</v>
+        <v>1713757413</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +3938,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +3957,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1711172650</v>
+        <v>1713849356</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +3971,7 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +3990,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1711172672</v>
+        <v>1713849385</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3893,6 +4004,7 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4023,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1711172697</v>
+        <v>1713849410</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4037,7 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4056,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1711172745</v>
+        <v>1713849460</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4070,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4089,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1711172780</v>
+        <v>1713849485</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3989,6 +4103,7 @@
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4122,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1711172812</v>
+        <v>1713917219</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4136,7 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4155,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1711255825</v>
+        <v>1713932288</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4169,7 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4188,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1711255857</v>
+        <v>1713932315</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4202,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4221,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1711255884</v>
+        <v>1713932351</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4117,6 +4235,7 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4254,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1711255937</v>
+        <v>1713932407</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4268,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4287,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1711255975</v>
+        <v>1713932431</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4301,7 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4320,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1711256021</v>
+        <v>1713932466</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4334,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4353,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1711339667</v>
+        <v>1714016935</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4367,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4386,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1711339709</v>
+        <v>1714016962</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4400,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4419,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1711339743</v>
+        <v>1714016990</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4433,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4452,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1711339792</v>
+        <v>1714017036</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4466,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4485,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1711339823</v>
+        <v>1714017064</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4499,7 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4518,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1711339857</v>
+        <v>1714089568</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4532,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4551,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1711430251</v>
+        <v>1714102842</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4565,7 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4584,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1711430280</v>
+        <v>1714102863</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4598,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4617,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1711430305</v>
+        <v>1714102887</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,6 +4631,7 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4650,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1711430364</v>
+        <v>1714102953</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4664,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4683,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1711430390</v>
+        <v>1714102974</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4565,6 +4697,7 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4716,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1711430421</v>
+        <v>1714103008</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4730,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
